--- a/pricing/Clean_and_Green_Pricing_Workbook.xlsx
+++ b/pricing/Clean_and_Green_Pricing_Workbook.xlsx
@@ -33,13 +33,16 @@
     <definedName name="P2Mob">Assumptions!$B$13</definedName>
     <definedName name="P3Mob">Assumptions!$B$14</definedName>
     <definedName name="P4Mob">Assumptions!$B$15</definedName>
-    <definedName name="AppHrs">Assumptions!$B$16</definedName>
-    <definedName name="AppMob">Assumptions!$B$17</definedName>
-    <definedName name="OvsHrs">Assumptions!$B$18</definedName>
-    <definedName name="OvsMob">Assumptions!$B$19</definedName>
-    <definedName name="SprAudHrs">Assumptions!$B$20</definedName>
-    <definedName name="SprHeadHrs">Assumptions!$B$21</definedName>
-    <definedName name="BHyveHrs">Assumptions!$B$22</definedName>
+    <definedName name="VisitsPerSeason">Assumptions!$B$16</definedName>
+    <definedName name="VisitHrs">Assumptions!$B$17</definedName>
+    <definedName name="VisitMob">Assumptions!$B$18</definedName>
+    <definedName name="AppHrs">Assumptions!$B$19</definedName>
+    <definedName name="AppMob">Assumptions!$B$20</definedName>
+    <definedName name="OvsHrs">Assumptions!$B$21</definedName>
+    <definedName name="OvsMob">Assumptions!$B$22</definedName>
+    <definedName name="SprAudHrs">Assumptions!$B$23</definedName>
+    <definedName name="SprHeadHrs">Assumptions!$B$24</definedName>
+    <definedName name="BHyveHrs">Assumptions!$B$25</definedName>
     <definedName name="Glyphosate">'Materials Catalog'!$I$3</definedName>
     <definedName name="Surfactant">'Materials Catalog'!$I$4</definedName>
     <definedName name="Tenacity">'Materials Catalog'!$I$5</definedName>
@@ -78,7 +81,7 @@
     <definedName name="P4_Total">'Phase 4 - Establish'!$F$19</definedName>
     <definedName name="P4_Mat">'Phase 4 - Establish'!$F11</definedName>
     <definedName name="P4_Lab">'Phase 4 - Establish'!$F17</definedName>
-    <definedName name="Summer_Total">'Summer Services'!$H$21</definedName>
+    <definedName name="Summer_Total">'Summer Services'!$F$31</definedName>
     <definedName name="Sprinkler_Total">'Sprinkler Services'!$H$12</definedName>
     <definedName name="OVE_Total">'Overseeding'!$F$24</definedName>
     <definedName name="OVE_Mat">'Overseeding'!$F16</definedName>
@@ -216,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -284,8 +287,24 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -293,15 +312,8 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1249,11 +1261,11 @@
           <t>MATERIALS SUBTOTAL (with markup)</t>
         </is>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="37">
         <f>E7+E8+E9</f>
         <v/>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="29">
         <f>F7+F8+F9</f>
         <v/>
       </c>
@@ -1299,7 +1311,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="n"/>
+      <c r="A15" s="30" t="n"/>
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Field labor (per 1,000 sq ft)</t>
@@ -1309,7 +1321,7 @@
         <f>P4Hrs hr/1,000 sf</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="38">
         <f>P4Hrs*(LawnSize/1000)</f>
         <v/>
       </c>
@@ -1321,10 +1333,10 @@
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="G15" s="33" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="n"/>
+      <c r="A16" s="30" t="n"/>
       <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Mobilization / setup</t>
@@ -1335,7 +1347,7 @@
           <t>Fixed hrs/job</t>
         </is>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="38">
         <f>P4Mob</f>
         <v/>
       </c>
@@ -1347,7 +1359,7 @@
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="G16" s="33" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -1355,13 +1367,13 @@
           <t>LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="29">
         <f>F15+F16</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>PHASE 4  |  ESTABLISHMENT (FOLLOW-UP FEED + 2ND TENACITY) - PHASE TOTAL</t>
         </is>
@@ -1539,7 +1551,7 @@
           <t>MATERIALS TOTAL (w/ markup)</t>
         </is>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="29">
         <f>SUM(C3:C6)</f>
         <v/>
       </c>
@@ -1550,7 +1562,7 @@
           <t>LABOR TOTAL</t>
         </is>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="29">
         <f>SUM(D3:D6)</f>
         <v/>
       </c>
@@ -1594,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1895,31 +1907,31 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Single-App Labor (per 1,000 sq ft)</t>
+          <t>Visits per Season</t>
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>visits</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Time per 1k sqft for a single fert/biostim/PGR/etc. application.</t>
+          <t>Physical visits per year for the annual program (5-6 typical).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Single-App Mobilization Hours</t>
+          <t>Visit Labor (per 1,000 sq ft)</t>
         </is>
       </c>
       <c r="B17" s="22" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
@@ -1928,18 +1940,18 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Drive, mix tank, walkthrough per single-visit service.</t>
+          <t>Time per 1k sqft per physical visit (3-5 products tank-mixed).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Overseeding Labor (per 1,000 sq ft)</t>
+          <t>Visit Mobilization Hours</t>
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
@@ -1948,18 +1960,18 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Dethatch + aerate + seed + Tenacity + peat top-dress.</t>
+          <t>Drive, mix tank, walkthrough per visit.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Overseeding Mobilization Hours</t>
+          <t>Single-App Labor (per 1,000 sq ft)</t>
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
@@ -1968,18 +1980,18 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Equipment pickup/return + customer walk-through.</t>
+          <t>Used only for one-off service quotes outside the annual program.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler Audit Labor (flat)</t>
+          <t>Single-App Mobilization Hours</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1988,18 +2000,18 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Catch cup audit + diagnose + write DU report.</t>
+          <t>Used only for one-off service quotes outside the annual program.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler Repair Labor (per head)</t>
+          <t>Overseeding Labor (per 1,000 sq ft)</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
@@ -2008,25 +2020,85 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Replace a single sprinkler head incl. minor digging.</t>
+          <t>Dethatch + aerate + seed + Tenacity + peat top-dress.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Overseeding Mobilization Hours</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Equipment pickup/return + customer walk-through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Sprinkler Audit Labor (flat)</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Catch cup audit + diagnose + write DU report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sprinkler Repair Labor (per head)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Replace a single sprinkler head incl. minor digging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>B-Hyve Smart Controller Install</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B25" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>FREE labor per Ryan's offer; baked into controller markup.</t>
         </is>
@@ -3322,23 +3394,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summer Services  |  À la carte / annual program menu</t>
+          <t>Summer Services  |  Annual program (5-6 bundled visits/season)</t>
         </is>
       </c>
     </row>
@@ -3349,103 +3420,72 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="50" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Year-round application menu. Set '# Apps' per row to match the customer's plan (full annual program, single application, etc.). Material cost scales by lawn size; labor scales per application using AppHrs (field) + AppMob (per visit).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+          <t>Annual program. Materials are calculated per product based on apps/year (not all applied at once). Labor is calculated per physical visit -- ~6 visits/season with 3-5 products tank-mixed per visit. Customer pays for visits, not per tank-mixed product. Adjust 'Visits per Season' on the Assumptions tab to match the customer's plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Material Plan (per product, scales by apps/year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>$ / 1,000 sf</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t># Apps</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Mat. cost (raw)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Mat. (w/ markup)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Labor (total)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Service Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Pre-emergent (Prodiamine, spring + fall)</t>
-        </is>
-      </c>
-      <c r="C6" s="9">
-        <f>PreEm</f>
-        <v/>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="9">
-        <f>C6*D6*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="F6" s="10">
-        <f>E6*(1+Markup)</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D6*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H6" s="10">
-        <f>F6+G6</f>
-        <v/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Pre-emergent (Prodiamine, spring + fall)</t>
+        </is>
+      </c>
+      <c r="C7" s="9">
+        <f>PreEm</f>
+        <v/>
+      </c>
+      <c r="D7" s="28" t="n">
         <v>2</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Slow-release fertilizer application</t>
-        </is>
-      </c>
-      <c r="C7" s="9">
-        <f>SlowFert</f>
-        <v/>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>4</v>
       </c>
       <c r="E7" s="9">
         <f>C7*D7*(LawnSize/1000)</f>
@@ -3455,30 +3495,27 @@
         <f>E7*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G7" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D7*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H7" s="10">
-        <f>F7+G7</f>
-        <v/>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>Visits 1 + 5</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sulfate of Potash (K boost)</t>
+          <t>Slow-release fertilizer</t>
         </is>
       </c>
       <c r="C8" s="9">
-        <f>KBoost</f>
+        <f>SlowFert</f>
         <v/>
       </c>
       <c r="D8" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="9">
         <f>C8*D8*(LawnSize/1000)</f>
@@ -3488,30 +3525,27 @@
         <f>E8*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G8" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D8*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H8" s="10">
-        <f>F8+G8</f>
-        <v/>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>Visits 1, 3, 5, 6</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Iron / Ferromec foliar (deep green)</t>
+          <t>Sulfate of Potash (K boost)</t>
         </is>
       </c>
       <c r="C9" s="9">
-        <f>Iron</f>
+        <f>KBoost</f>
         <v/>
       </c>
       <c r="D9" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="9">
         <f>C9*D9*(LawnSize/1000)</f>
@@ -3521,26 +3555,23 @@
         <f>E9*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G9" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D9*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H9" s="10">
-        <f>F9+G9</f>
-        <v/>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>Visit 3 -- pre-summer</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Humic + Fulvic biostimulant</t>
+          <t>Iron / Ferromec foliar (deep green)</t>
         </is>
       </c>
       <c r="C10" s="9">
-        <f>Humic</f>
+        <f>Iron</f>
         <v/>
       </c>
       <c r="D10" s="28" t="n">
@@ -3554,26 +3585,23 @@
         <f>E10*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G10" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D10*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H10" s="10">
-        <f>F10+G10</f>
-        <v/>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Visits 2 + 4</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Liquid Kelp biostimulant</t>
+          <t>Humic + Fulvic biostimulant</t>
         </is>
       </c>
       <c r="C11" s="9">
-        <f>Kelp</f>
+        <f>Humic</f>
         <v/>
       </c>
       <c r="D11" s="28" t="n">
@@ -3587,26 +3615,23 @@
         <f>E11*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G11" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D11*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H11" s="10">
-        <f>F11+G11</f>
-        <v/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Visits 2 + 5</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Hydretain wetting agent (UT clay)</t>
+          <t>Liquid Kelp biostimulant</t>
         </is>
       </c>
       <c r="C12" s="9">
-        <f>Hydretain</f>
+        <f>Kelp</f>
         <v/>
       </c>
       <c r="D12" s="28" t="n">
@@ -3620,30 +3645,27 @@
         <f>E12*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G12" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D12*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H12" s="10">
-        <f>F12+G12</f>
-        <v/>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>Visits 2 + 4 (tank w/ iron)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>PGR / Primo Maxx (less mowing)</t>
+          <t>Hydretain wetting agent</t>
         </is>
       </c>
       <c r="C13" s="9">
-        <f>PGR</f>
+        <f>Hydretain</f>
         <v/>
       </c>
       <c r="D13" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9">
         <f>C13*D13*(LawnSize/1000)</f>
@@ -3653,30 +3675,27 @@
         <f>E13*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G13" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D13*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>F13+G13</f>
-        <v/>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>Visit 3 -- pre-summer</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Grub prevention (Imidacloprid, mid-July)</t>
+          <t>PGR / Primo Maxx (less mowing)</t>
         </is>
       </c>
       <c r="C14" s="9">
-        <f>Grub</f>
+        <f>PGR</f>
         <v/>
       </c>
       <c r="D14" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="9">
         <f>C14*D14*(LawnSize/1000)</f>
@@ -3686,26 +3705,23 @@
         <f>E14*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G14" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D14*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H14" s="10">
-        <f>F14+G14</f>
-        <v/>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Visits 2, 3, 4 (May-July)</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Fall winterizer (high-K)</t>
+          <t>Grub prevention (Imidacloprid)</t>
         </is>
       </c>
       <c r="C15" s="9">
-        <f>Winter</f>
+        <f>Grub</f>
         <v/>
       </c>
       <c r="D15" s="28" t="n">
@@ -3719,30 +3735,27 @@
         <f>E15*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G15" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D15*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H15" s="10">
-        <f>F15+G15</f>
-        <v/>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Visit 4 -- mid-July</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Fungicide (dollar spot, brown patch)</t>
+          <t>Fall winterizer (high-K)</t>
         </is>
       </c>
       <c r="C16" s="9">
-        <f>Fungicide</f>
+        <f>Winter</f>
         <v/>
       </c>
       <c r="D16" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="9">
         <f>C16*D16*(LawnSize/1000)</f>
@@ -3752,119 +3765,217 @@
         <f>E16*(1+Markup)</f>
         <v/>
       </c>
-      <c r="G16" s="9">
-        <f>(AppHrs*(LawnSize/1000)+AppMob)*D16*LaborRate</f>
-        <v/>
-      </c>
-      <c r="H16" s="10">
-        <f>F16+G16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>Visit 6 -- late Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Fungicide (as-needed)</t>
+        </is>
+      </c>
+      <c r="C17" s="9">
+        <f>Fungicide</f>
+        <v/>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <f>C17*D17*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="F17" s="10">
+        <f>E17*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>Add 1-2 apps if disease pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>MATERIALS SUBTOTAL (w/ markup)</t>
+        </is>
+      </c>
+      <c r="F19" s="29">
+        <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Visit-Based Labor (per Assumptions tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Calc / cell</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Visits per season</t>
+        </is>
+      </c>
+      <c r="C23" s="31">
+        <f>VisitsPerSeason</f>
+        <v/>
+      </c>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>Adjust on Assumptions tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Hours per visit</t>
+        </is>
+      </c>
+      <c r="C24" s="32">
+        <f>VisitHrs*(LawnSize/1000)+VisitMob</f>
+        <v/>
+      </c>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="26">
+        <f> VisitHrs * (LawnSize/1000) + VisitMob</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Cost per visit</t>
+        </is>
+      </c>
+      <c r="C25" s="33">
+        <f>C24*LaborRate</f>
+        <v/>
+      </c>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>LABOR SUBTOTAL (visits x cost/visit)</t>
+        </is>
+      </c>
+      <c r="F26" s="29">
+        <f>VisitsPerSeason*C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Diagnostic add-on (flat fee, not per-sqft)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Flat fee</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Cost (raw)</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Cost (w/ markup)</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Service Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
+    <row r="29">
+      <c r="A29" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Soil test + analysis (Logan Labs)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C29" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D29" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="9">
-        <f>C19*D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>(no labor)</t>
-        </is>
-      </c>
-      <c r="H19" s="10">
-        <f>F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>SUMMER SERVICES TOTAL</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="13">
-        <f>H6+H7+H8+H9+H10+H11+H12+H13+H14+H15+H16+H19</f>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="10">
+        <f>C29*D29</f>
+        <v/>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>$30 cost = $30 to customer. Edit C to charge the '$60 value' price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>ANNUAL PROGRAM TOTAL</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="13">
+        <f>F19+F26+F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Per sq ft cost (reference)</t>
+        </is>
+      </c>
+      <c r="F32" s="35">
+        <f>F31/LawnSize</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3970,10 +4081,10 @@
       <c r="D6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="9">
@@ -4119,7 +4230,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>SPRINKLER SERVICES TOTAL</t>
         </is>
@@ -4434,11 +4545,11 @@
           <t>MATERIALS SUBTOTAL (with markup)</t>
         </is>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="37">
         <f>E7+E8+E9+E10+E11+E14</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="29">
         <f>F7+F8+F9+F10+F11+F14</f>
         <v/>
       </c>
@@ -4484,7 +4595,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="n"/>
+      <c r="A20" s="30" t="n"/>
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Field labor (per 1,000 sq ft)</t>
@@ -4494,7 +4605,7 @@
         <f>OvsHrs hr/1,000 sf</f>
         <v/>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="38">
         <f>OvsHrs*(LawnSize/1000)</f>
         <v/>
       </c>
@@ -4506,10 +4617,10 @@
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="G20" s="33" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="n"/>
+      <c r="A21" s="30" t="n"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Mobilization / setup</t>
@@ -4520,7 +4631,7 @@
           <t>Fixed hrs/job</t>
         </is>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="38">
         <f>OvsMob</f>
         <v/>
       </c>
@@ -4532,7 +4643,7 @@
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="G21" s="33" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -4540,13 +4651,13 @@
           <t>LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="29">
         <f>F20+F21</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>FALL OVERSEEDING  |  AERATE + OVERSEED + STARTER + TENACITY - PHASE TOTAL</t>
         </is>
@@ -4784,11 +4895,11 @@
           <t>MATERIALS SUBTOTAL (with markup)</t>
         </is>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="37">
         <f>E7+E8+E11</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="29">
         <f>F7+F8+F11</f>
         <v/>
       </c>
@@ -4834,7 +4945,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n"/>
+      <c r="A17" s="30" t="n"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Field labor (per 1,000 sq ft)</t>
@@ -4844,7 +4955,7 @@
         <f>P1Hrs hr/1,000 sf</f>
         <v/>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="38">
         <f>P1Hrs*(LawnSize/1000)</f>
         <v/>
       </c>
@@ -4856,10 +4967,10 @@
         <f>D17*E17</f>
         <v/>
       </c>
-      <c r="G17" s="33" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="n"/>
+      <c r="A18" s="30" t="n"/>
       <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Mobilization / setup</t>
@@ -4870,7 +4981,7 @@
           <t>Fixed hrs/job</t>
         </is>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="38">
         <f>P1Mob</f>
         <v/>
       </c>
@@ -4882,7 +4993,7 @@
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="G18" s="33" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -4890,13 +5001,13 @@
           <t>LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="29">
         <f>F17+F18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>PHASE 1  |  KILL (GLYPHOSATE BURN-DOWN) - PHASE TOTAL</t>
         </is>
@@ -5108,11 +5219,11 @@
           <t>MATERIALS SUBTOTAL (with markup)</t>
         </is>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="37">
         <f>E9+E10</f>
         <v/>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="29">
         <f>F9+F10</f>
         <v/>
       </c>
@@ -5158,7 +5269,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="n"/>
+      <c r="A16" s="30" t="n"/>
       <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Field labor (per 1,000 sq ft)</t>
@@ -5168,7 +5279,7 @@
         <f>P2Hrs hr/1,000 sf</f>
         <v/>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="38">
         <f>P2Hrs*(LawnSize/1000)</f>
         <v/>
       </c>
@@ -5180,10 +5291,10 @@
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="G16" s="33" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n"/>
+      <c r="A17" s="30" t="n"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Mobilization / setup</t>
@@ -5194,7 +5305,7 @@
           <t>Fixed hrs/job</t>
         </is>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="38">
         <f>P2Mob</f>
         <v/>
       </c>
@@ -5206,7 +5317,7 @@
         <f>D17*E17</f>
         <v/>
       </c>
-      <c r="G17" s="33" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -5214,13 +5325,13 @@
           <t>LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="29">
         <f>F16+F17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>PHASE 2  |  PREP (SCALP, DETHATCH, AERATE) - PHASE TOTAL</t>
         </is>
@@ -5466,11 +5577,11 @@
           <t>MATERIALS SUBTOTAL (with markup)</t>
         </is>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="37">
         <f>E7+E8+E9+E10+E11</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="29">
         <f>F7+F8+F9+F10+F11</f>
         <v/>
       </c>
@@ -5516,7 +5627,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n"/>
+      <c r="A17" s="30" t="n"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Field labor (per 1,000 sq ft)</t>
@@ -5526,7 +5637,7 @@
         <f>P3Hrs hr/1,000 sf</f>
         <v/>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="38">
         <f>P3Hrs*(LawnSize/1000)</f>
         <v/>
       </c>
@@ -5538,10 +5649,10 @@
         <f>D17*E17</f>
         <v/>
       </c>
-      <c r="G17" s="33" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="n"/>
+      <c r="A18" s="30" t="n"/>
       <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Mobilization / setup</t>
@@ -5552,7 +5663,7 @@
           <t>Fixed hrs/job</t>
         </is>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="38">
         <f>P3Mob</f>
         <v/>
       </c>
@@ -5564,7 +5675,7 @@
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="G18" s="33" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -5572,13 +5683,13 @@
           <t>LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="29">
         <f>F17+F18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>PHASE 3  |  SEED + STARTER FERTILIZER + TENACITY - PHASE TOTAL</t>
         </is>

--- a/pricing/Clean_and_Green_Pricing_Workbook.xlsx
+++ b/pricing/Clean_and_Green_Pricing_Workbook.xlsx
@@ -57,7 +57,7 @@
     <definedName name="Humic">'Materials Catalog'!$I$14</definedName>
     <definedName name="Kelp">'Materials Catalog'!$I$15</definedName>
     <definedName name="Hydretain">'Materials Catalog'!$I$16</definedName>
-    <definedName name="PGR">'Materials Catalog'!$I$17</definedName>
+    <definedName name="RGS">'Materials Catalog'!$I$17</definedName>
     <definedName name="Grub">'Materials Catalog'!$I$18</definedName>
     <definedName name="Winter">'Materials Catalog'!$I$19</definedName>
     <definedName name="Fungicide">'Materials Catalog'!$I$20</definedName>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Primo Maxx (PGR / Trinexapac-ethyl)</t>
+          <t>N-ext RGS (Root Growth Stimulant)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Greene County</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="G17" s="24" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="I17" s="10">
         <f>G17/E17*H17</f>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="J17" s="26" t="inlineStr">
         <is>
-          <t>Plant Growth Regulator. Rate: 0.25 oz / 1,000 sq ft. Slows top growth.</t>
+          <t>Humic + seaweed extract root stimulant. Rate: 6 oz / 1,000 sq ft. The N-ext line.</t>
         </is>
       </c>
     </row>
@@ -3687,15 +3687,15 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>PGR / Primo Maxx (less mowing)</t>
+          <t>Root growth stimulant (N-ext RGS)</t>
         </is>
       </c>
       <c r="C14" s="9">
-        <f>PGR</f>
+        <f>RGS</f>
         <v/>
       </c>
       <c r="D14" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="9">
         <f>C14*D14*(LawnSize/1000)</f>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="G14" s="26" t="inlineStr">
         <is>
-          <t>Visits 2, 3, 4 (May-July)</t>
+          <t>Visits 2-5 monthly (Apr-Oct)</t>
         </is>
       </c>
     </row>

--- a/pricing/Clean_and_Green_Pricing_Workbook.xlsx
+++ b/pricing/Clean_and_Green_Pricing_Workbook.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer Services" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprinkler Services" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overseeding" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 - Kill" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 - Prep" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3 - Seed" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 4 - Establish" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Total" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dethatching" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 - Kill" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 - Prep" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3 - Seed" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 4 - Establish" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Total" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="LawnSize">Assumptions!$B$3</definedName>
@@ -40,9 +41,11 @@
     <definedName name="AppMob">Assumptions!$B$20</definedName>
     <definedName name="OvsHrs">Assumptions!$B$21</definedName>
     <definedName name="OvsMob">Assumptions!$B$22</definedName>
-    <definedName name="SprAudHrs">Assumptions!$B$23</definedName>
-    <definedName name="SprHeadHrs">Assumptions!$B$24</definedName>
-    <definedName name="BHyveHrs">Assumptions!$B$25</definedName>
+    <definedName name="DethHrs">Assumptions!$B$23</definedName>
+    <definedName name="DethMob">Assumptions!$B$24</definedName>
+    <definedName name="SprAudHrs">Assumptions!$B$25</definedName>
+    <definedName name="SprHeadHrs">Assumptions!$B$26</definedName>
+    <definedName name="BHyveHrs">Assumptions!$B$27</definedName>
     <definedName name="Glyphosate">'Materials Catalog'!$I$3</definedName>
     <definedName name="Surfactant">'Materials Catalog'!$I$4</definedName>
     <definedName name="Tenacity">'Materials Catalog'!$I$5</definedName>
@@ -86,6 +89,9 @@
     <definedName name="OVE_Total">'Overseeding'!$F$24</definedName>
     <definedName name="OVE_Mat">'Overseeding'!$F16</definedName>
     <definedName name="OVE_Lab">'Overseeding'!$F22</definedName>
+    <definedName name="DET_Total">'Dethatching'!$F$19</definedName>
+    <definedName name="DET_Mat">'Dethatching'!$F11</definedName>
+    <definedName name="DET_Lab">'Dethatching'!$F17</definedName>
     <definedName name="GrandTotal">'Project Total'!$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1100,6 +1106,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase 3  |  Seed + Starter Fertilizer + Tenacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Scope of Work</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Apply starter fertilizer, then broadcast Valkyrie seed at 10 lb / 1,000 sq ft in two directions. Tank-mix Tenacity with non-ionic surfactant and apply at 0.18 oz / 1,000 sq ft for 21 days of pre-emergent weed protection. Top-dress lightly with peat moss to retain moisture, then begin the watering schedule (light 2-3x daily until germination).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Materials  (per 1,000 sq ft items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>$ / 1,000 sq ft</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t># Apps</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Cost (raw)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Cost (w/ markup)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Starter fertilizer (24-25-4)</t>
+        </is>
+      </c>
+      <c r="C7" s="9">
+        <f>Starter</f>
+        <v/>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9">
+        <f>C7*D7*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="F7" s="10">
+        <f>E7*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Valkyrie tall fescue seed</t>
+        </is>
+      </c>
+      <c r="C8" s="9">
+        <f>Seed</f>
+        <v/>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <f>C8*D8*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="F8" s="10">
+        <f>E8*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G8" s="26" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Tenacity at-seeding pre-emergent</t>
+        </is>
+      </c>
+      <c r="C9" s="9">
+        <f>Tenacity</f>
+        <v/>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <f>C9*D9*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="F9" s="10">
+        <f>E9*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Non-Ionic Surfactant (Tenacity tank)</t>
+        </is>
+      </c>
+      <c r="C10" s="9">
+        <f>Surfactant</f>
+        <v/>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <f>C10*D10*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>E10*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G10" s="26" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Peat moss top-dress</t>
+        </is>
+      </c>
+      <c r="C11" s="9">
+        <f>Peat</f>
+        <v/>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9">
+        <f>C11*D11*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="F11" s="10">
+        <f>E11*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G11" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>MATERIALS SUBTOTAL (with markup)</t>
+        </is>
+      </c>
+      <c r="E13" s="37">
+        <f>E7+E8+E9+E10+E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>F7+F8+F9+F10+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Hours basis</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Field labor (per 1,000 sq ft)</t>
+        </is>
+      </c>
+      <c r="C17" s="7">
+        <f>P3Hrs hr/1,000 sf</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>P3Hrs*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="E17" s="9">
+        <f>LaborRate</f>
+        <v/>
+      </c>
+      <c r="F17" s="10">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Mobilization / setup</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Fixed hrs/job</t>
+        </is>
+      </c>
+      <c r="D18" s="38">
+        <f>P3Mob</f>
+        <v/>
+      </c>
+      <c r="E18" s="9">
+        <f>LaborRate</f>
+        <v/>
+      </c>
+      <c r="F18" s="10">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>LABOR SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="F19" s="29">
+        <f>F17+F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>PHASE 3  |  SEED + STARTER FERTILIZER + TENACITY - PHASE TOTAL</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="13">
+        <f>F13+F19</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1398,7 +1761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001B4D1F"/>
@@ -1606,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2047,11 +2410,11 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler Audit Labor (flat)</t>
+          <t>Dethatching Labor (per 1,000 sq ft)</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
@@ -2060,18 +2423,18 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Catch cup audit + diagnose + write DU report.</t>
+          <t>Power dethatch + rake/haul thatch debris.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Sprinkler Repair Labor (per head)</t>
+          <t>Dethatching Mobilization Hours</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
@@ -2080,25 +2443,65 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Replace a single sprinkler head incl. minor digging.</t>
+          <t>Equipment pickup/return + customer walk-through.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Sprinkler Audit Labor (flat)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Catch cup audit + diagnose + write DU report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sprinkler Repair Labor (per head)</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Replace a single sprinkler head incl. minor digging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>B-Hyve Smart Controller Install</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B27" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>FREE labor per Ryan's offer; baked into controller markup.</t>
         </is>
@@ -4686,6 +5089,304 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5D6A7"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dethatching  |  Power-rake + thatch removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Scope of Work</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Standalone power-dethatching service for thinning lawns with a thick thatch layer (typically &gt;1/2 inch). Power-rake removes built-up thatch so water, air, and nutrients can reach the soil. Crew hauls all debris. Most lawns only need this every 3-5 years; best paired with overseeding when scheduled in fall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Materials  (per 1,000 sq ft items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>$ / 1,000 sq ft</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t># Apps</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Cost (raw)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Cost (w/ markup)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Materials  (per-job / one-time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Cost each</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Cost (raw)</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Cost (w/ markup)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Power dethatcher rental (4-hr)</t>
+        </is>
+      </c>
+      <c r="C9" s="9">
+        <f>Dethatcher</f>
+        <v/>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="10">
+        <f>E9*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G9" s="26" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>MATERIALS SUBTOTAL (with markup)</t>
+        </is>
+      </c>
+      <c r="E11" s="37">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="F11" s="29">
+        <f>F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Hours basis</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Field labor (per 1,000 sq ft)</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
+        <f>DethHrs hr/1,000 sf</f>
+        <v/>
+      </c>
+      <c r="D15" s="38">
+        <f>DethHrs*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="E15" s="9">
+        <f>LaborRate</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Mobilization / setup</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Fixed hrs/job</t>
+        </is>
+      </c>
+      <c r="D16" s="38">
+        <f>DethMob</f>
+        <v/>
+      </c>
+      <c r="E16" s="9">
+        <f>LaborRate</f>
+        <v/>
+      </c>
+      <c r="F16" s="10">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LABOR SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="F17" s="29">
+        <f>F15+F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>DETHATCHING  |  POWER-RAKE + THATCH REMOVAL - PHASE TOTAL</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="13">
+        <f>F11+F17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5033,7 +5734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D32"/>
@@ -5355,361 +6056,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phase 3  |  Seed + Starter Fertilizer + Tenacity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>Scope of Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Apply starter fertilizer, then broadcast Valkyrie seed at 10 lb / 1,000 sq ft in two directions. Tank-mix Tenacity with non-ionic surfactant and apply at 0.18 oz / 1,000 sq ft for 21 days of pre-emergent weed protection. Top-dress lightly with peat moss to retain moisture, then begin the watering schedule (light 2-3x daily until germination).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>Materials  (per 1,000 sq ft items)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>$ / 1,000 sq ft</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t># Apps</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Cost (raw)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Cost (w/ markup)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Starter fertilizer (24-25-4)</t>
-        </is>
-      </c>
-      <c r="C7" s="9">
-        <f>Starter</f>
-        <v/>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="9">
-        <f>C7*D7*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="F7" s="10">
-        <f>E7*(1+Markup)</f>
-        <v/>
-      </c>
-      <c r="G7" s="26" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Valkyrie tall fescue seed</t>
-        </is>
-      </c>
-      <c r="C8" s="9">
-        <f>Seed</f>
-        <v/>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9">
-        <f>C8*D8*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="F8" s="10">
-        <f>E8*(1+Markup)</f>
-        <v/>
-      </c>
-      <c r="G8" s="26" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Tenacity at-seeding pre-emergent</t>
-        </is>
-      </c>
-      <c r="C9" s="9">
-        <f>Tenacity</f>
-        <v/>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9">
-        <f>C9*D9*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="F9" s="10">
-        <f>E9*(1+Markup)</f>
-        <v/>
-      </c>
-      <c r="G9" s="26" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Non-Ionic Surfactant (Tenacity tank)</t>
-        </is>
-      </c>
-      <c r="C10" s="9">
-        <f>Surfactant</f>
-        <v/>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9">
-        <f>C10*D10*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
-        <f>E10*(1+Markup)</f>
-        <v/>
-      </c>
-      <c r="G10" s="26" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Peat moss top-dress</t>
-        </is>
-      </c>
-      <c r="C11" s="9">
-        <f>Peat</f>
-        <v/>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9">
-        <f>C11*D11*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
-        <f>E11*(1+Markup)</f>
-        <v/>
-      </c>
-      <c r="G11" s="26" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>MATERIALS SUBTOTAL (with markup)</t>
-        </is>
-      </c>
-      <c r="E13" s="37">
-        <f>E7+E8+E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F13" s="29">
-        <f>F7+F8+F9+F10+F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Hours basis</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="n"/>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Field labor (per 1,000 sq ft)</t>
-        </is>
-      </c>
-      <c r="C17" s="7">
-        <f>P3Hrs hr/1,000 sf</f>
-        <v/>
-      </c>
-      <c r="D17" s="38">
-        <f>P3Hrs*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="E17" s="9">
-        <f>LaborRate</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="30" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="n"/>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Mobilization / setup</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Fixed hrs/job</t>
-        </is>
-      </c>
-      <c r="D18" s="38">
-        <f>P3Mob</f>
-        <v/>
-      </c>
-      <c r="E18" s="9">
-        <f>LaborRate</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>D18*E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="30" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>LABOR SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="F19" s="29">
-        <f>F17+F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>PHASE 3  |  SEED + STARTER FERTILIZER + TENACITY - PHASE TOTAL</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="13">
-        <f>F13+F19</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/pricing/Clean_and_Green_Pricing_Workbook.xlsx
+++ b/pricing/Clean_and_Green_Pricing_Workbook.xlsx
@@ -86,9 +86,9 @@
     <definedName name="P4_Lab">'Phase 4 - Establish'!$F17</definedName>
     <definedName name="Summer_Total">'Summer Services'!$F$31</definedName>
     <definedName name="Sprinkler_Total">'Sprinkler Services'!$H$12</definedName>
-    <definedName name="OVE_Total">'Overseeding'!$F$24</definedName>
-    <definedName name="OVE_Mat">'Overseeding'!$F16</definedName>
-    <definedName name="OVE_Lab">'Overseeding'!$F22</definedName>
+    <definedName name="OVE_Total">'Overseeding'!$F$26</definedName>
+    <definedName name="OVE_Mat">'Overseeding'!$F17</definedName>
+    <definedName name="OVE_Lab">'Overseeding'!$F24</definedName>
     <definedName name="DET_Total">'Dethatching'!$F$19</definedName>
     <definedName name="DET_Mat">'Dethatching'!$F11</definedName>
     <definedName name="DET_Lab">'Dethatching'!$F17</definedName>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Dethatch + aerate + seed + Tenacity + peat top-dress.</t>
+          <t>Aerate + seed + starter + Tenacity + peat top-dress (dethatch is a separate line).</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4680,7 +4680,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fall Overseeding  |  Aerate + Overseed + Starter + Tenacity</t>
+          <t>Fall Overseeding  |  Dethatch + Aerate + Overseed + Starter + Tenacity</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Lighter than full renovation. Core aerate, broadcast seed at half the renovation rate (~5 lb / 1,000 sq ft), apply starter fertilizer + Tenacity, light peat moss top-dress. Customer's existing lawn keeps growing through germination. Aug-Oct only.</t>
+          <t>Lighter than full renovation. Power-dethatch first, then core aerate, broadcast seed at half the renovation rate (~5 lb / 1,000 sq ft), apply starter fertilizer + Tenacity, light peat moss top-dress. Customer's existing lawn keeps growing through germination. Aug-Oct only. Dethatching is broken out as its own labor line + equipment rental so we can track that revenue separately.</t>
         </is>
       </c>
     </row>
@@ -4922,11 +4922,11 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Core aerator rental (4-hr)</t>
+          <t>Power dethatcher rental (4-hr)</t>
         </is>
       </c>
       <c r="C14" s="9">
-        <f>Aerator</f>
+        <f>Dethatcher</f>
         <v/>
       </c>
       <c r="D14" s="28" t="n">
@@ -4942,100 +4942,100 @@
       </c>
       <c r="G14" s="26" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Core aerator rental (4-hr)</t>
+        </is>
+      </c>
+      <c r="C15" s="9">
+        <f>Aerator</f>
+        <v/>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>E15*(1+Markup)</f>
+        <v/>
+      </c>
+      <c r="G15" s="26" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>MATERIALS SUBTOTAL (with markup)</t>
         </is>
       </c>
-      <c r="E16" s="37">
-        <f>E7+E8+E9+E10+E11+E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="29">
-        <f>F7+F8+F9+F10+F11+F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="E17" s="37">
+        <f>E7+E8+E9+E10+E11+E14+E15</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>F7+F8+F9+F10+F11+F14+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Hours basis</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Field labor (per 1,000 sq ft)</t>
-        </is>
-      </c>
-      <c r="C20" s="7">
-        <f>OvsHrs hr/1,000 sf</f>
-        <v/>
-      </c>
-      <c r="D20" s="38">
-        <f>OvsHrs*(LawnSize/1000)</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>LaborRate</f>
-        <v/>
-      </c>
-      <c r="F20" s="10">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="30" t="n"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Mobilization / setup</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Fixed hrs/job</t>
-        </is>
+          <t>Field labor (per 1,000 sq ft)</t>
+        </is>
+      </c>
+      <c r="C21" s="7">
+        <f>OvsHrs hr/1,000 sf</f>
+        <v/>
       </c>
       <c r="D21" s="38">
-        <f>OvsMob</f>
+        <f>OvsHrs*(LawnSize/1000)</f>
         <v/>
       </c>
       <c r="E21" s="9">
@@ -5049,37 +5049,88 @@
       <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Dethatching field labor (per 1,000 sq ft)</t>
+        </is>
+      </c>
+      <c r="C22" s="7">
+        <f>DethHrs hr/1,000 sf</f>
+        <v/>
+      </c>
+      <c r="D22" s="38">
+        <f>DethHrs*(LawnSize/1000)</f>
+        <v/>
+      </c>
+      <c r="E22" s="9">
+        <f>LaborRate</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Mobilization / setup</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Fixed hrs/job</t>
+        </is>
+      </c>
+      <c r="D23" s="38">
+        <f>OvsMob</f>
+        <v/>
+      </c>
+      <c r="E23" s="9">
+        <f>LaborRate</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="F22" s="29">
-        <f>F20+F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>FALL OVERSEEDING  |  AERATE + OVERSEED + STARTER + TENACITY - PHASE TOTAL</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="13">
-        <f>F16+F22</f>
+      <c r="F24" s="29">
+        <f>F21+F22+F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>FALL OVERSEEDING  |  DETHATCH + AERATE + OVERSEED + STARTER + TENACITY - PHASE TOTAL</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="13">
+        <f>F17+F24</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
